--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -599,7 +599,7 @@
         <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/2026/dandiya-night.jpg</v>
+        <v>assets/images/events/2026/Dandiya 2026.jpg</v>
       </c>
       <c r="O4" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -599,7 +599,7 @@
         <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/2026/Dandiya 2026.jpg</v>
+        <v>assets/images/events/2026/Dandiya Flyer Sponsors 10-1-2026.jpg</v>
       </c>
       <c r="O4" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -599,7 +599,7 @@
         <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/2026/Dandiya Flyer Sponsors 10-1-2026.jpg</v>
+        <v>assets/images/events/Dandiya 2026.jpg</v>
       </c>
       <c r="O4" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -599,7 +599,7 @@
         <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/Dandiya 2026.jpg</v>
+        <v>assets/images/events/2026/Dandiya 2026.jpg</v>
       </c>
       <c r="O4" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -599,7 +599,7 @@
         <v>assets/images/events/2026/2026 Daniya.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/2026/Dandiya 2026.jpg</v>
+        <v>assets/images/events/2026/Dandiya 2026 Sponsors.jpg</v>
       </c>
       <c r="O4" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -507,7 +507,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>previous</v>
+        <v/>
       </c>
       <c r="B3" t="str">
         <v>Event</v>
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>current</v>
+        <v>previous</v>
       </c>
       <c r="B4" t="str">
         <v>Event</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>future</v>
+        <v>current</v>
       </c>
       <c r="B11" t="str">
         <v>Event</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>future</v>
       </c>
       <c r="B12" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -884,7 +884,7 @@
         <v>Performance</v>
       </c>
       <c r="C10" t="str">
-        <v>Abhangvani</v>
+        <v>Bhakti Rang</v>
       </c>
       <c r="D10" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -931,19 +931,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>current</v>
+        <v>Future</v>
       </c>
       <c r="B11" t="str">
         <v>Event</v>
       </c>
       <c r="C11" t="str">
-        <v>Bondla and Kanya Pujan</v>
+        <v>Diwali</v>
       </c>
       <c r="D11" t="str">
-        <v>October</v>
+        <v>November</v>
       </c>
       <c r="E11" t="str">
-        <v>17</v>
+        <v/>
       </c>
       <c r="F11" t="str">
         <v>2026</v>
@@ -961,13 +961,13 @@
         <v>TBD</v>
       </c>
       <c r="K11" t="str">
-        <v>भोंडला – कडकडीत पारंपारिक खेळ आणि गोडगोष्टींचा आनंद, कन्या पूजन – पवित्रतेचे आणि सन्मानाचे प्रतीक; Sankalp Marathi Mandal या पारंपारिक उत्सवांचा आनंद हर्षोल्हासाने साजरा करत आहे—चला, सांस्कृतिक उत्सवाचा अनुभव एकत्र घेऊया! </v>
+        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>assets/images/events/2026/2026 Bondla.jpeg</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -979,65 +979,12 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>future</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Event</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Diwali</v>
-      </c>
-      <c r="D12" t="str">
-        <v>November</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v>2026</v>
-      </c>
-      <c r="G12" t="str">
-        <v>MA</v>
-      </c>
-      <c r="H12" t="str">
-        <v>MA</v>
-      </c>
-      <c r="I12" t="str">
-        <v>sankalpmarathimandal@gmail.com</v>
-      </c>
-      <c r="J12" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="K12" t="str">
-        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+        <v>WhatsApp Image 2026-10-23 at 10.40.28 AM.jpeg</v>
       </c>
       <c r="N11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>WhatsApp Image 2026-10-23 at 10.40.28 AM.jpeg</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+        <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+        <v/>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -967,10 +967,10 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>file:///Users/vedant/Downloads/2026%20Diwali.jpeg</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+        <v>2026-Diwali.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>2026-Diwali.jpeg</v>
+        <v>blob:https://web.whatsapp.com/de10660e-2016-4d43-935b-372c6523d383</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>blob:https://web.whatsapp.com/de10660e-2016-4d43-935b-372c6523d383</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -970,7 +970,7 @@
         <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
+        <v>https://raw.githubusercontent.com/sankalpmarathimandal-debug/SankalpMarathiMandalWebsite/main/assets/images/events/2026/Diwali%20flyer.jpeg</v>
       </c>
       <c r="O11" t="str">
         <v/>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -931,7 +931,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Future</v>
+        <v>Futurw</v>
       </c>
       <c r="B11" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -566,7 +566,7 @@
         <v>Event</v>
       </c>
       <c r="C4" t="str">
-        <v>Dandiya Night</v>
+        <v>Diwali</v>
       </c>
       <c r="D4" t="str">
         <v>October</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Futurw</v>
+        <v>Future</v>
       </c>
       <c r="B11" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -566,7 +566,7 @@
         <v>Event</v>
       </c>
       <c r="C4" t="str">
-        <v>Diwali</v>
+        <v>Dandiya Night</v>
       </c>
       <c r="D4" t="str">
         <v>October</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -566,7 +566,7 @@
         <v>Event</v>
       </c>
       <c r="C4" t="str">
-        <v>Dandiya Night</v>
+        <v>Diwali</v>
       </c>
       <c r="D4" t="str">
         <v>October</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>previous</v>
+        <v>Future</v>
       </c>
       <c r="B4" t="str">
         <v>Event</v>
@@ -569,37 +569,37 @@
         <v>Diwali</v>
       </c>
       <c r="D4" t="str">
-        <v>October</v>
+        <v>November</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v>2026</v>
       </c>
       <c r="G4" t="str">
-        <v>Freeman-Kennedy School</v>
+        <v>MA</v>
       </c>
       <c r="H4" t="str">
-        <v>70 Boardman St, Norfolk, MA -02056</v>
+        <v>MA</v>
       </c>
       <c r="I4" t="str">
         <v>sankalpmarathimandal@gmail.com</v>
       </c>
       <c r="J4" t="str">
-        <v>6:00 PM to 10:00 PM</v>
+        <v>TBD</v>
       </c>
       <c r="K4" t="str">
-        <v>धुंद गरबा – पारंपारिक वेशभूषा आणि उर्जा भरलेले नृत्य, दांडियाची खणखण – टाळ्यांच्या गजरात हरवून जाणारा आनंद, आणि ढोल-ताशांचा ठेका – मनाला थिरकायला लावणारी ऊर्जा; Sankalp Marathi Mandal या सर्वात मोठ्या भव्य उत्सवाचा आनंद साजरा करत आहे—चला, दांडिया नाईटचा अनुभव एकत्र घेऊया!</v>
+        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
       </c>
       <c r="L4" t="str">
         <v>धुंद गरबा – पारंपारिक वेशभूषा आणि उर्जा भरलेले नृत्य, दांडियाची खणखण – टाळ्यांच्या गजरात हरवून जाणारा आनंद, आणि ढोल-ताशांचा ठेका – मनाला थिरकायला लावणारी ऊर्जा; Sankalp Marathi Mandal या सर्वात मोठ्या भव्य उत्सवाचा आनंद साजरा करत आहे—चला, दांडिया नाईटचा अनुभव एकत्र घेऊया!</v>
       </c>
       <c r="M4" t="str">
-        <v>assets/images/events/2026/2026 Daniya.jpeg</v>
+        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
       </c>
       <c r="N4" t="str">
-        <v>assets/images/events/2026/Dandiya 2026 Sponsors.jpg</v>
+        <v>https://raw.githubusercontent.com/sankalpmarathimandal-debug/SankalpMarathiMandalWebsite/main/assets/images/events/2026/Diwali%20flyer.jpeg</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v>दक्षिणेकडून उत्तरेकडे प्रवास सुरू होतो सूर्यदेवाचा. तिळगुळ घ्या गोड गोड बोला म्हणत एकत्र साजरा करुया सण मकरसंक्रांतीचा.</v>
       </c>
       <c r="L5" t="str">
-        <v>मकर संक्रांत हा नव्या उर्जेचा, आशेचा आणि आनंदाचा सण आहे. सूर्य मकर राशीत प्रवेश करतो आणि उत्तरायणाची सुरुवात होते. या मंगल प्रसंगी आपण सर्वांनी एकत्र येऊन आपली परंपरा, संस्कृती आणि आपुलकी जपण्याचा संकल्प करूया. तिळगूळ, पतंगांची रंगीबेरंगी उधळण, गोड गाणी आणि आपुलकीच्या भेटीगाठींनी नटलेला मकर संक्रांत २०२६ कार्यक्रम सर्वांसाठी आनंददायी ठरणार आहे.</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v>assets/images/events/2026/makar-sankrant.jpg</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Future</v>
+        <v>future</v>
       </c>
       <c r="B4" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>future</v>
+        <v/>
       </c>
       <c r="B4" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -560,7 +560,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>future</v>
       </c>
       <c r="B4" t="str">
         <v>Event</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Future</v>
+        <v/>
       </c>
       <c r="B11" t="str">
         <v>Event</v>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -929,62 +929,9 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v>Event</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Diwali</v>
-      </c>
-      <c r="D11" t="str">
-        <v>November</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v>2026</v>
-      </c>
-      <c r="G11" t="str">
-        <v>MA</v>
-      </c>
-      <c r="H11" t="str">
-        <v>MA</v>
-      </c>
-      <c r="I11" t="str">
-        <v>sankalpmarathimandal@gmail.com</v>
-      </c>
-      <c r="J11" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="K11" t="str">
-        <v>दिवाळी—अंधारावर प्रकाशाचा विजय, सुख-समृद्धी आणि नवचैतन्य घेऊन येणारा सण. घरोघरी रंगोळी, दिवे आणि गोड पदार्थांची उत्सवाची रंगत अनुभवताना, चला, आनंद आणि उत्साहाने हा मंगलसोहळा एकत्र साजरा करूया! 杖✨</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>assets/images/events/2026/2026 Diwali.jpeg</v>
-      </c>
-      <c r="N11" t="str">
-        <v>https://raw.githubusercontent.com/sankalpmarathimandal-debug/SankalpMarathiMandalWebsite/main/assets/images/events/2026/Diwali%20flyer.jpeg</v>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q10"/>
   </ignoredErrors>
 </worksheet>
 </file>